--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99263</v>
+        <v>99264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99263</v>
+        <v>99264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99263</v>
+        <v>99264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99263</v>
+        <v>99264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99263</v>
+        <v>99264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550703</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136551288</v>
       </c>
       <c r="B3" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551335</v>
       </c>
       <c r="B4" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136551345</v>
       </c>
       <c r="B5" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136552379</v>
       </c>
       <c r="B6" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082343</v>
+        <v>7082342</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082342</v>
+        <v>7082343</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082343</v>
+        <v>7082342</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082342</v>
+        <v>7082343</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082343</v>
+        <v>7082342</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082342</v>
+        <v>7082343</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99279</v>
+        <v>99280</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082343</v>
+        <v>7082342</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082342</v>
+        <v>7082343</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550703</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136551288</v>
       </c>
       <c r="B3" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551335</v>
       </c>
       <c r="B4" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136551345</v>
       </c>
       <c r="B5" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136552379</v>
       </c>
       <c r="B6" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082343</v>
+        <v>7082342</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35265-2026 artfynd.xlsx
+++ b/artfynd/A 35265-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136550703</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136551288</v>
       </c>
       <c r="B3" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -895,7 +895,7 @@
         <v>136551335</v>
       </c>
       <c r="B4" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136551345</v>
       </c>
       <c r="B5" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136552379</v>
       </c>
       <c r="B6" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136533931</v>
       </c>
       <c r="B7" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136551043</v>
       </c>
       <c r="B8" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136533480</v>
       </c>
       <c r="B9" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136551695</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136539003</v>
       </c>
       <c r="B11" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136551242</v>
       </c>
       <c r="B12" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136551573</v>
       </c>
       <c r="B13" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136551013</v>
       </c>
       <c r="B14" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136548513</v>
       </c>
       <c r="B15" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136551014</v>
       </c>
       <c r="B16" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136551036</v>
       </c>
       <c r="B17" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136551260</v>
       </c>
       <c r="B18" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>524130</v>
       </c>
       <c r="R18" t="n">
-        <v>7082342</v>
+        <v>7082343</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>136552541</v>
       </c>
       <c r="B19" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
